--- a/_work/analysis/02_сравнение_поручение.xlsx
+++ b/_work/analysis/02_сравнение_поручение.xlsx
@@ -506,12 +506,12 @@
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Доверитель: №35 Кызылорда — КГУ «Управление сельского хозяйства и земельных отношений Кызылординской области» (преамбула); №43 Мангистау — ГУ «Управление сельского хозяйства и земельных отношений Мангистауской области» (преамбула). Поверенный: №35 Кызылорда — «Поверенный агент», АО «Социально-предпринимательская корпорация «Байконыр (Байконур)» (преамбула); №43 Мангистау — «Поверенный (агент)», АО «СПК «Каспий», определен по договору о государственных закупках услуг и Правилам (преамбула). Различаются организационно-правовая форма Доверителя (КГУ / ГУ), сами Доверители и Поверенные, а также обозначение Поверенного («Поверенный агент» / «Поверенный (агент)»).</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -536,12 +536,12 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: преамбула («принимая во внимание», пп. 1)-10)) — 10 актов (БК РК от 15.03.2025 №171-VIII; Закон о республиканском бюджете на 2026–2028 от 08.12.2025 №239-VIII; Постановление Правительства РК от 10.12.2025 №1074; Приказы МФ РК от 26.06.2025 №325, от 31.12.2025 №843, от 27.06.2025 №328; Приказ и.о. МФ РК от 16.05.2025 №236; Приказ №53 от 16.06.2025; Постановление акимата Кызылординской области от 12.12.2025 №233; Трехсторонний кредитный договор от 29 мая 2026 №9МИО1610); п. 1.2 — договор о государственных закупках услуг [номер и дата не указаны]; п. 3.1 — Программа 087. №43 Мангистау: преамбула — Правила микрокредитования и лизинга (Приказ №53 от 16.06.2025) и договор о госзакупках услуг №12 от 22.07.2025; разд. «Основные условия займа и общие требования», пп. 8–9 — условия финансирования по Правилам (приказ от 16 июня 2025 № 53), общие требования по приложению 4. Общее: оба договора ссылаются на Приказ №53 от 16.06.2025 и на договор о госзакупках услуг. Только в №35: перечень из 10 актов, Программа 087, трехсторонний кредитный договор; только в №43: указан номер и дата договора госзакупок (№12 от 22.07.2025).</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -567,12 +567,12 @@
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: разд. 1 — Доверитель предоставляет Поверенному агенту займ; цель — микрокредитование претендентов для проектов в сельских населенных пунктах и малых городах и лизинг сельхозтехники и оборудования; сумма 5 600 000 000 тенге; ставка 1 % годовых; срок 10 лет; период освоения 12 месяцев с момента перечисления бюджетного кредита местному исполнительному органу; льготный период по основному долгу — не более 28 месяцев; п. 1.3 — Поверенный агент действует от имени и за счет Доверителя (определение конечных заемщиков, мониторинг финансового состояния, обслуживание займа, расчеты, мониторинг залога, взыскание задолженности, хранение документов); п. 1.4 — расчеты на основании договоров займа между Доверителем, Поверенным агентом и конечными заемщиками. №43 Мангистау: п. 1.1 — Поверенный оказывает услугу по обслуживанию бюджетного кредита: организует и сопровождает кредитные сделки между Доверителем/Заимодателем, Поверенным и Заемщиком; Доверитель оплачивает стоимость услуг. В ячейке №43 отсутствуют сумма, ставка, срок займа и перечень поручаемых действий «от имени и за счет Доверителя» (в №35 они есть); в ячейке №35 нет условия об оплате Доверителем стоимости услуг в составе предмета (в №43 — п. 1.1).</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -606,12 +606,12 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: п. 3.8 — вправе привлекать третьих лиц для выполнения «Задания» по доверенности Доверителя; п. 4.1, пп. 1)-13) — обязанности Поверенного агента (обслуживание займа, расчеты, мониторинг, кредитные досье, подготовка договоров займа и залога по Приложениям №2 и №3, сбор документов по Приложениям №4, №4/1, №4/2, принятие решения о выдаче займа, направление Доверителю договоров займа и залога для заключения, прием платежей для направления Доверителю, отчеты уполномоченным органам, посткредитное обслуживание, хранение документов и ежеквартальный мониторинг); п. 4.4 — взыскание с Заемщика в судебном порядке; п. 4.5 — иные функции по законодательству, Договору, договору госзакупок, техспецификации. №43 Мангистау: разд. «Основные функции, права и обязанности сторон» — функции Доверителя (подписание договоров микрокредита, залога и/или гарантии по прил. 5, 6, 7; учет и перечисление средств; оплата услуг и возмещение расходов по ст. 849 ГК РК; выдача доверенностей для суда в течение 10 календарных дней со дня письменного запроса; участие в Кредитной комиссии Поверенного; регистрация кредитных договоров по п. 614 Правил исполнения бюджета) и функции Поверенного (прием пакета документов по прил. 2, оценка соответствия, подготовка договоров по прил. 5, 6, 7, досудебная работа с проблемными Заемщиками — просрочка более 90 календарных дней и иные случаи, взыскание по законодательству и внутренним документам; Кредитная комиссия по письменному поручению «Заказчика» решает о судебном взыскании, мировом/медиативном соглашении, обращении взыскания на залог); права Поверенного — отступить от указаний Доверителя, если необходимо в его интересах и нельзя заранее запросить его либо ответ не получен своевременно; определять заемщиков-физлиц и заключать с ними кредитные договоры по поручению. Различия: решение о выдаче займа — Поверенный агент (№35, п. 4.1 пп. 8)) / Кредитная комиссия Поверенного с участием Доверителя (№43); привлечение третьих лиц — только в №35 (п. 3.8); право отступить от указаний Доверителя, перечень «проблемных» заемщиков и обязанности Доверителя (доверенности, регистрация договоров) — только в №43; договоры займа/залога в №35 готовит Поверенный агент и направляет Доверителю для заключения (п. 4.1), в №43 договоры подписывает Доверитель (прил. 5, 6, 7).</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено (положения о том, кто принимает решение о выдаче займа — Поверенный агент (№35, п. 4.1 пп. 8)) или Кредитная комиссия Поверенного с участием Доверителя (№43) — относятся к разным моделям, но взаимоисключение из текста ячеек не следует)</t>
         </is>
       </c>
     </row>
@@ -647,12 +647,12 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: п. 3.2, п. 4.1 пп. 7), 8) — порядок микрокредитования и лизинга по Приказу №53 от 16.06.2025; приоритетные направления (за исключением несельскохозяйственных проектов) определяются на основе скрининга; решение о выдаче займа принимает Поверенный агент; документы потенциальных заемщиков — по Приложениям №4, №4/1, №4/2; п. 3.6 — заем не предоставляется на рефинансирование просроченной задолженности; пп. 3.4, 3.5, 3.7, 3.9 — ставка конечным заемщикам 2,5% годовых, период освоения 6 месяцев с момента перечисления микрокредита, условия — по договору займа (Приложение №2); пп. 3.7 и 3.9 дублируют друг друга. №43 Мангистау: п. 1.9 — преимущественная поддержка кооперативам и переработке сельхозпродукции; п. 1.10 — приостановка приема и рассмотрения заявок при отсутствии финансирования (кроме возвратных средств); разд. «Порядок финансирования», абз. 1–3 — бумажная и/или электронная заявка через личный кабинет с документами по прил. 2, проверка по госбазам, ЭЦП; абз. 4–6 — проверка документов 3 рабочих дня со дня регистрации, мотивированный отказ; абз. 7–9 — решение по микрокредиту и по лизингу в течение 15 рабочих дней со дня регистрации; разд. «Основные условия займа и общие требования», пп. 1–7 — претенденты на микрокредит (граждане РК, безработные, самозанятые и бездействующие ИП, лица в неоплачиваемом семейном предпринимательстве, ЛПХ с доходом ниже прожиточного минимума, кооперативы и их члены, ИП), п. 2 — на лизинг только кооперативы и члены кооперативов, п. 3 — регистрация в качестве ИП при одобрении, п. 4 — на переработку только ИП и кооперативы, п. 5 — постоянная регистрация не менее 12 месяцев, пп. 6–7 — требования к ИП/юрлицам и кооперативам. Сроки рассмотрения, перечень претендентов, личный кабинет, приоритеты и приостановка приема — только в №43; запрет рефинансирования просрочки, ставка 2,5% и срок освоения 6 месяцев конечным заемщиком — только в №35.</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -679,12 +679,12 @@
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Сумма: №35 Кызылорда — 5 600 000 000 тенге безналичным расчетом на расчетный счет Поверенного агента (п. 2.1); №43 Мангистау — 2 400 000 000 тенге по бюджетной программе «Предоставление микрокредитов сельскому населению для масштабирования проекта по повышению доходов сельского населения» на указанный счет (Казначейство) (п. 1.2). Срок перечисления: №35 — в течение пяти рабочих дней после подписания Договора (п. 2.2); в №43 срок перечисления Доверителем в ячейке не указан. Период освоения: №35 — 12 месяцев с момента перечисления бюджетного кредита местному исполнительному органу (п. 3.3); №43 — 300 календарных дней с момента перечисления Доверителем на счет Поверенного (п. 1.7). Только в №43: перечисление микрокредита на счет претендента в течение 5 рабочих дней после регистрации договора залога в уполномоченном органе; по лизингу — приобретение техники Поверенным у продавца (разд. «Порядок финансирования», абз. 10–11); повторное микрокредитование за счет возвращенных средств по Правилам (абз. 13).</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -708,12 +708,12 @@
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Размер: №35 Кызылорда — 1,0% от общей суммы выданных займов согласно постановлению акимата Кызылординской области от 04.02.2026 №19 (п. 2.8); №43 Мангистау — 2,49% годовых (с НДС) от остатка основного долга по выданным кредитам на дату окончания календарного года (п. 1.4). Периодичность: №35 — ежемесячно, не позднее 10 числа месяца, следующего за отчетным, на основании подписанного Акта об оказанных услугах (п. 2.9); №43 — один раз в год в течение 15 календарных дней после полного освоения суммы бюджетного кредита, на основании акта сверки (прил. 9) и акта выполненных работ (прил. 10) (п. 1.4). Кто платит: №35 — оплату осуществляет местный исполнительный орган по вопросам сельского хозяйства за счет средств местного бюджета (п. 2.6), по п. 2.9 — Доверитель; №43 — Доверитель (п. 1.4).</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: п. 2.3 — средства по п. 2.1 подлежат возврату Поверенным агентом Доверителю; п. 2.4 — выплата начисленного вознаграждения по Займу один раз в год 15 мая, начиная с 15 декабря 2026 года, последняя выплата 15 мая 2036 года (Приложение №1); п. 2.5 — возврат вознаграждения от конечных заемщиков ежегодно не позднее 10 июля, начиная с 2027 года; п. 2.7 — неиспользованные средства возвращаются в течение 3 рабочих дней после окончания периода освоения (получатель в тексте назван «Кредитору»); п. 2.10 — зачисление на счет РГУ «Департамент государственных доходов по Кызылординской области КГД МФ РК» (БИК KKMFKZ2A, Кбе 11); КБК 601 106, 201 706, 601 208, 204 118; Приложение №1 — график: 12 платежей с 15.12.2026 по 15.05.2036, основной долг с 15.09.2028, итого 5 901 065 535,56 тенге. №43 Мангистау: пп. 1.5–1.6 — Поверенный по графику погашения (прил. 1) перечисляет средства от Заемщиков в Управление государственных доходов (Департамент государственных доходов по Мангистауской области), КНП 911, КБК 501 106, 201 706 и 201 713, 204 118; разд. «Порядок финансирования», абз. 14 — учет и хранение оригиналов правоустанавливающих и идентификационных документов на залоговое имущество осуществляет Поверенный; функции Поверенного, абз. 6 — принимает платежи Заемщиков для направления в местный бюджет; «Поверенный (агент) обязуется», абз. 3 — неиспользованные средства возвращаются Доверителю в течение 3 рабочих дней после окончания периода освоения с уведомлением. Совпадает срок возврата неиспользованных средств (3 рабочих дня: №35 п. 2.7, №43 абз. 3). Различаются получатель платежей (ДГД по Кызылординской / Мангистауской области), КБК (601 106 / 501 106 для основного долга; вознаграждение: 201 706 / 201 706 и 201 713), график и даты платежей (даты приведены только в №35).</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -773,12 +773,12 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: п. 4.1 пп. 14) — ежемесячно до 5 числа месяца, следующего за отчетным, отчет о целевом использовании микрокредитов и отчет о мониторинге в местный исполнительный орган по сельскому хозяйству (Приложения №6, №7, №8, №9); п. 4.1 пп. 15) — ежемесячно до 10 числа АКТ выполненных работ (Приложение №10); п. 5.1 — контроль за целевым использованием займа конечным заемщиком. №43 Мангистау: функции Поверенного, абз. 5, 7–8 — хранение кредитных досье и копий документов, мониторинг целевого использования в сроки, установленные договором микрокредита, ежемесячный отчет о целевом использовании в уполномоченный орган; «Поверенный (агент) обязуется», абз. 4–5 — учет по каждому Конечному заемщику; информация Доверителю ежемесячно до 5 числа месяца, следующего за отчетным, и ежеквартально до 15 числа месяца, следующего за отчетным, по форме приложения 8 к Правилам (приказ и.о. МФ РК от 16.05.2025 №236). Совпадает срок ежемесячной отчетности (до 5 числа). Только в №35: акт выполненных работ ежемесячно до 10 числа; только в №43: ежеквартальная информация до 15 числа по приложению 8 к Правилам (приказ №236).</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -806,12 +806,12 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Нецелевое использование средств Поверенным: №35 Кызылорда — возврат суммы и штраф 25% от суммы нецелевого использования в течение 7 рабочих дней с даты получения требования (п. 5.2); №43 Мангистау — возврат суммы и штраф 0,1% в течение 7 рабочих дней после обнаружения факта (п. 5.2). Просрочка возврата: №35 — пеня 0,1% от суммы задолженности за каждый календарный день; в течение 90 дней не более 0,1% от суммы просроченного платежа в день, после 90 дней не более 0,03% в день, но не более 10% от суммы выданного займа за каждый год действия Договора (п. 5.3); №43 — не более 0,1% в день в течение 90 дней, далее не более 0,03% в день, не более 10% от суммы, предоставленной Доверителем за каждый год (п. 5.3). Неосвоенные средства: №35 — пеня 5% от суммы неосвоенной части за каждый день просрочки, максимум — сумма, неиспользованная заемщиком за период освоения (п. 5.4); №43 — пеня 0,1% в день, максимум 10% от суммы, неиспользованной Поверенным за период освоения (п. 5.4). Общая норма: №35, п. 5.5 — каждая сторона отвечает за неисполнение по Договору и законодательству. Только в №43: перечень случаев, когда Поверенный не отвечает (п. 5.1, пп. 5.1.1–5.1.4: отказ потенциального Заемщика, неправомерность сделок Заемщика, гибель залога вследствие форс-мажора или действий Заемщика/Залогодателя, неисполнение обязательств Заемщиком/Залогодателем/Гарантом).</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: п. 10.3 — вступает в силу с момента подписания, в части взаиморасчетов действует до полного исполнения обязательств; продление по соглашению Сторон. №43 Мангистау: п. 1.3 и пп. 7.1–7.2 — срок оказания услуг с подписания и до полного исполнения Заемщиками обязательств по договорам микрокредита; вступает в силу со дня подписания. Общее: вступление в силу с подписания. Различается момент окончания: исполнение обязательств сторон по взаиморасчетам (№35) / исполнение обязательств Заемщиками по микрокредиту (№43); условие о продлении по соглашению — только в №35.</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -861,12 +861,12 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда, п. 9.2 — односторонний отказ от исполнения Договора не допускается; иных оснований прекращения/расторжения нет. №43 Мангистау (разд. «Основные функции, права и обязанности сторон», абз. «Стороны вправе расторгнуть Договор») — расторжение по инициативе любой из Сторон либо по обоюдному волеизъявлению путем подписания Соглашения о расторжении и полного взаиморасчета, срок уведомления не указан; также п. 6.2 (см. строку «Форс-мажор») — при невозможности устранить отсутствие разрешений Поверенный инициирует расторжение.</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда (п. 9.2: односторонний отказ от исполнения Договора не допускается) и №43 Мангистау (расторжение по инициативе любой из Сторон) — положения взаимоисключающие по существу: право расторгнуть по инициативе одной стороны допускается в №43 и запрещено в №35.</t>
         </is>
       </c>
     </row>
@@ -890,12 +890,12 @@
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда, пп. 8.1–8.5 — освобождение от ответственности при непреодолимой силе, возникшей после заключения; извещение в течение 10 дней с даты возникновения, по требованию — документ компетентного госоргана; извещение о прекращении — в течение 3 рабочих дней; срок исполнения отодвигается соразмерно. №43 Мангистау, пп. 6.1–6.4 — перечень обстоятельств (стихийные бедствия, эпидемии, военные конфликты, теракты, забастовки, акты Правительства/Нацбанка и др.); сроки отодвигаются по обоюдному согласию на время действия событий; отсутствие разрешений, лицензий, одобрений госорганов не является форс-мажором, при невозможности устранения Поверенный инициирует расторжение (п. 6.2); стороны немедленно письменно извещают о начале и окончании, ссылающаяся сторона предоставляет документ компетентного госоргана. Различия: срок извещения — 10 дней (№35) / немедленно (№43); срок исполнения — соразмерно (№35) / по обоюдному согласию (№43); перечень обстоятельств и исключение по разрешениям — только в №43.</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: пп. 6.1–6.3 — переговоры; претензия рассматривается в течение 5 рабочих дней с момента направления либо в указанный в ней срок; неурегулированные споры — в судебном порядке; пп. 4.2, 4.3 — споры между Поверенным агентом и претендентами: переговоры, затем суд по законодательству РК; п. 9.3 — предварительное рассмотрение, иначе по законодательству РК и Договору. №43 Мангистау: пп. 8.1–8.2 — предварительное рассмотрение разногласий; неурегулированные споры — по законодательству РК, подсудность не указана. Претензионный срок 5 рабочих дней и споры с претендентами — только в №35.</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда (пп. 3.9, 4.1 пп. 6), 7), 14), 15); п. 10.5): в тексте упомянуты Приложения №1 (график погашения), №2 (договор о предоставлении займа), №3 (договор залога), №4, №4/1, №4/2 (документы потенциальных заемщиков), №6, №7, №8, №9 (отчеты), №10 (акт); все приложения — неотъемлемая часть; в файле фактически присутствует только Приложение №1. №43 Мангистау (п. 9.3): Договор содержит Приложения № 1 – 13 (в файле присутствуют приложения 2, 3, 4, 8, 9, 10; приложение 1 — график погашения, 5–7 — формы договоров микрокредита, залога, гарантии упомянуты по тексту). Различаются состав и нумерация: в №35 Приложение №2 — договор займа, №3 — договор залога, №6–9 — отчеты, №10 — акт; в №43 приложение 2 — пакет документов (по функциям Поверенного), 3 — требования к залоговому обеспечению, 4 — общие требования, 5–7 — формы договоров микрокредита, залога, гарантии, 8 — форма информации по кредиту, 9 — акт сверки, 10 — акт выполненных работ (по ячейкам других строк). Совпадает: Приложение 1 — график погашения в обоих договорах. Общее число приложений указано только в №43 (13).</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -973,12 +973,12 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда: разд. «Адреса и реквизиты» — БИН/ИИК/БИК сторон, подписи руководителей и м.п. [данные сторон]. №43 Мангистау: разд. «Адреса и реквизиты сторон» — Доверитель: ГУ «Управление сельского хозяйства и земельных отношений Мангистауской области», г. Актау, 23 мкр, здание № 14; Поверенный: АО «СПК «Каспий», г. Актау, 9а мкр, здание № 7/1; подписи Мураталиев Д. и Арғынбай К. (в заполненном экземпляре). Реквизиты сторон различаются (разные организации и адреса); печать (м.п.) указана только в ячейке №35.</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1000,12 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Условие есть только в №35 Кызылорда (пп. 7.1–7.5): уведомления — заказным письмом, факсом, электронной почтой или иными ИКТ, либо курьером; отправленные по ИКТ считаются доставленными в день отправки; вступают в силу после доставки или в указанный день (что позднее); при смене адреса/реквизитов — письменное уведомление; приведены адреса и телефоны сторон. В №43 Мангистау отдельного раздела об уведомлениях в ячейке нет («—»).</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда (пп. 9.1, 10.4): изменения и дополнения действительны при письменной форме, подписи уполномоченных представителей и печатях; являются приложениями к Договору. №43 Мангистау (п. 9.1): изменение условий только по взаимному согласию письменным дополнительным соглашением. Общее: письменная форма. Различия: требование печатей и подписей уполномоченных представителей — только в №35; условие «по взаимному согласию» и форма «дополнительное соглашение» — только в №43.</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -1054,12 +1054,12 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>№35 Кызылорда (п. 10.2): 6 экземпляров (3 на государственном, 3 на русском), по 2 для Доверителя, Поверенного агента и для регистрации КГУ «Управление экономики и финансов Кызылординской области»; при разночтениях приоритет у русского текста. №43 Мангистау (п. 9.2): три экземпляра на государственном и русском языках (по одному каждой Стороне, третий — регистрирующему органу); при разночтении приоритет у русского текста. Совпадает: языки (государственный и русский) и приоритет русского текста. Различаются число экземпляров (6 / 3) и регистрирующий орган (в №35 назван КГУ «Управление экономики и финансов Кызылординской области», в №43 — «регистрирующий орган» без наименования).</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -1081,12 +1081,12 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Условие есть только в №35 Кызылорда (пп. 9.4, 10.1): все, что не предусмотрено Договором, регулируется законодательством РК. В №43 Мангистау в ячейке отсутствует («—»); при этом в №43 в других строках есть отсылки к законодательству РК (пп. 7.1–7.2, 8.1–8.2), но общей нормы о субсидиарном применении в ячейке нет.</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -1108,12 +1108,12 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Условие есть только в №43 Мангистау (п. 1.8): микрокредитование проектов по приобретению сельхозживотных — не более 40%, в сфере переработки — не менее 20% от общей суммы финансирования, предусмотренной для каждой области по плану финансирования. В №35 Кызылорда отсутствует («—»).</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -1135,12 +1135,12 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Условие есть только в №43 Мангистау (разд. «Порядок финансирования», абз. 12): обеспечение по залогу определяется по перечню требований к залоговому обеспечению согласно приложению 3. В ячейке №35 Кызылорда отдельного условия нет («—»), при том что в строке «Приложения» №35 упоминается Приложение №3 как договор залога (п. 4.1).</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -1162,12 +1162,12 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>Условие есть только в №43 Мангистау (разд. «Основные функции, права и обязанности сторон», «Поверенный (агент) не вправе»): Поверенный не вправе распространять персональные данные заемщиков, за исключением государственных или правовых органов по официальному письму. В №35 Кызылорда отсутствует («—»).</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>(не заполнено)</t>
+          <t>не выявлено</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="110" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1206,6 +1207,11 @@
           <t>Описание</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Примечание (квалификация)</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -1223,6 +1229,7 @@
           <t>Определение «Договор» дано дважды: как кредитный договор и как договор поручения</t>
         </is>
       </c>
+      <c r="D2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1240,6 +1247,7 @@
           <t>П. 2.4 одновременно устанавливает выплату 15 мая каждого года и первую выплату 15 декабря 2026 (не 15 мая); дата первой выплаты не укладывается в заявленную периодичность</t>
         </is>
       </c>
+      <c r="D3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -1257,6 +1265,7 @@
           <t>Ставка вознаграждения Поверенного: 2,49% годовых (с НДС) в п. 1.4 и 2,5% годовых в форме акта (прил. 10), на основании которого производится оплата по п. 1.4.</t>
         </is>
       </c>
+      <c r="D4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1274,6 +1283,7 @@
           <t>Доля переработки: «не менее 20%» от общей суммы финансирования в п. 1.8 и «не более 20%» в прил. 4.</t>
         </is>
       </c>
+      <c r="D5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -1291,6 +1301,7 @@
           <t>Сумма цифрами 2 400 000 000 не совпадает с суммой прописью («два миллиарда четыреста тысяч» = 2 000 400 000 по словесной записи) в одном пункте.</t>
         </is>
       </c>
+      <c r="D6" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1735,13 +1746,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:E1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
     <col width="45" customWidth="1" min="2" max="2"/>
     <col width="90" customWidth="1" min="3" max="3"/>
     <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="50" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1763,6 +1775,11 @@
       <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Результат автосверки</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Ручная сверка</t>
         </is>
       </c>
     </row>
